--- a/Result/profitability/4754.xlsx
+++ b/Result/profitability/4754.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM53"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7161,6 +7161,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4754</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>195</v>
+      </c>
+      <c r="D54" t="n">
+        <v>94</v>
+      </c>
+      <c r="E54" t="n">
+        <v>101</v>
+      </c>
+      <c r="F54" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="G54" t="n">
+        <v>47</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>24.32%</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>48</v>
+      </c>
+      <c r="K54" t="n">
+        <v>38</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N54" t="n">
+        <v>47.4575</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.3263157894736843</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.559999999999995</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.05195859549421544</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0.9399999999999977</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.01847121241894278</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
